--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,8 @@
           <t>Sant Parampra</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
+      <c r="D2" t="n">
+        <v>123456789</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -493,6 +491,37 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yug Interior</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Yug Interior</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>yug@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
         </is>
       </c>
     </row>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,82 +446,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>email</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>project</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sant Parampra</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sant Parampra</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>123456789</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>santparampra@gmail.com</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Yug Interior</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Yug Interior</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>yug@gmail.com</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Inactive</t>
         </is>
       </c>
     </row>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,52 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>email</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sant Parampra</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sant Parampra</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>santparampra@gmail.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1234567891</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
